--- a/multi/gemini_domain.xlsx
+++ b/multi/gemini_domain.xlsx
@@ -472,10 +472,10 @@
         </is>
       </c>
       <c r="B11" s="0" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C11" s="0" t="n">
-        <v>0.3</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="12">
